--- a/Reference/Complete Data Frame (Hormones, Behavior, Size, Gonads) GG.xlsx
+++ b/Reference/Complete Data Frame (Hormones, Behavior, Size, Gonads) GG.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fish Lab\Experiments\sex change single nuc POA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ggraham/Desktop/multiome_poa/Reference/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6D3D2B-2730-4E7D-9163-36F822BEE96F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EA4129-8D06-284B-A7C0-1E946C8336E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="105" yWindow="15" windowWidth="27000" windowHeight="14250" xr2:uid="{4C85D3C2-4423-4DD6-A968-B296FD30C807}"/>
+    <workbookView xWindow="100" yWindow="780" windowWidth="27000" windowHeight="14260" xr2:uid="{4C85D3C2-4423-4DD6-A968-B296FD30C807}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$J$2:$J$33</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$J$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet1!$J$2:$J$33</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="100">
   <si>
     <t>Fish</t>
   </si>
   <si>
-    <t>Total_Slides_With_Gonad</t>
-  </si>
-  <si>
     <t>A12D</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>Estimated_Volume_2.5x</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>T17D</t>
   </si>
   <si>
@@ -269,12 +257,6 @@
     <t>Expanded Partner</t>
   </si>
   <si>
-    <t>Dominant</t>
-  </si>
-  <si>
-    <t>Subordinate</t>
-  </si>
-  <si>
     <t>Female</t>
   </si>
   <si>
@@ -345,6 +327,15 @@
   </si>
   <si>
     <t>Behaviors_Per_Time</t>
+  </si>
+  <si>
+    <t>Total_Slides_With_God</t>
+  </si>
+  <si>
+    <t>Domint</t>
+  </si>
+  <si>
+    <t>Subordite</t>
   </si>
 </sst>
 </file>
@@ -430,7 +421,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
@@ -442,7 +433,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,9 +453,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -503,7 +493,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -609,7 +599,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -751,7 +741,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -760,111 +750,111 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04868345-CCCB-43F7-B0BB-81ED40AC86E5}">
   <dimension ref="A1:X33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="5" max="5" width="9.140625"/>
-    <col min="8" max="9" width="9.140625"/>
-    <col min="11" max="12" width="9.140625"/>
-    <col min="15" max="15" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="8.85546875" style="10"/>
+    <col min="5" max="5" width="9.1640625"/>
+    <col min="8" max="9" width="9.1640625"/>
+    <col min="11" max="12" width="9.1640625"/>
+    <col min="15" max="15" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="8.83203125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O1" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s">
+        <v>77</v>
+      </c>
+      <c r="S1" t="s">
+        <v>90</v>
+      </c>
+      <c r="T1" t="s">
+        <v>91</v>
+      </c>
+      <c r="U1" t="s">
+        <v>92</v>
+      </c>
+      <c r="V1" t="s">
+        <v>93</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" t="s">
-        <v>100</v>
-      </c>
-      <c r="K1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" t="s">
+      <c r="C2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="M1" t="s">
-        <v>63</v>
-      </c>
-      <c r="N1" t="s">
-        <v>64</v>
-      </c>
-      <c r="O1" t="s">
-        <v>51</v>
-      </c>
-      <c r="P1" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R1" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" t="s">
-        <v>94</v>
-      </c>
-      <c r="T1" t="s">
-        <v>95</v>
-      </c>
-      <c r="U1" t="s">
-        <v>96</v>
-      </c>
-      <c r="V1" t="s">
-        <v>97</v>
-      </c>
-      <c r="W1" s="10" t="s">
-        <v>98</v>
-      </c>
-      <c r="X1" s="10" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H2" s="6">
         <v>274</v>
@@ -922,27 +912,27 @@
         <v>6.7978812803962834</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2">
         <v>557</v>
@@ -950,7 +940,7 @@
       <c r="I3" s="2">
         <v>546</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="2">
         <f t="shared" ref="J3:J33" si="1">I3/H3</f>
         <v>0.98025134649910228</v>
       </c>
@@ -1001,27 +991,27 @@
         <v>6.2088599419687291</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H4" s="2">
         <v>274</v>
@@ -1029,7 +1019,7 @@
       <c r="I4" s="2">
         <v>746</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="2">
         <f t="shared" si="1"/>
         <v>2.7226277372262775</v>
       </c>
@@ -1080,27 +1070,27 @@
         <v>6.5822606661556602</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H5" s="2">
         <v>24</v>
@@ -1108,7 +1098,7 @@
       <c r="I5" s="2">
         <v>2</v>
       </c>
-      <c r="J5" s="11">
+      <c r="J5" s="2">
         <f t="shared" si="1"/>
         <v>8.3333333333333329E-2</v>
       </c>
@@ -1159,27 +1149,27 @@
         <v>5.925072875155351</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2">
         <v>571</v>
@@ -1187,7 +1177,7 @@
       <c r="I6" s="2">
         <v>543</v>
       </c>
-      <c r="J6" s="11">
+      <c r="J6" s="2">
         <f t="shared" si="1"/>
         <v>0.95096322241681264</v>
       </c>
@@ -1238,27 +1228,27 @@
         <v>6.5441054972494941</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H7" s="2">
         <v>162</v>
@@ -1266,7 +1256,7 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="11">
+      <c r="J7" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -1317,27 +1307,21 @@
         <v>6.0674744995801504</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D8" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2">
         <v>449</v>
@@ -1345,72 +1329,32 @@
       <c r="I8" s="2">
         <v>120</v>
       </c>
-      <c r="J8" s="11">
+      <c r="J8" s="2">
         <f t="shared" si="1"/>
         <v>0.267260579064588</v>
       </c>
-      <c r="K8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" t="s">
-        <v>53</v>
-      </c>
       <c r="M8" s="1">
         <v>1.669967369908504</v>
       </c>
       <c r="N8" s="1"/>
-      <c r="O8" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" t="s">
-        <v>53</v>
-      </c>
-      <c r="S8" t="s">
-        <v>53</v>
-      </c>
-      <c r="T8" t="s">
-        <v>53</v>
-      </c>
-      <c r="U8" t="s">
-        <v>53</v>
-      </c>
-      <c r="V8" t="s">
-        <v>53</v>
-      </c>
-      <c r="W8" t="s">
-        <v>53</v>
-      </c>
-      <c r="X8" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W8"/>
+      <c r="X8"/>
+    </row>
+    <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G9" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H9" s="2">
         <v>600</v>
@@ -1418,15 +1362,9 @@
       <c r="I9" s="2">
         <v>600</v>
       </c>
-      <c r="J9" s="11">
+      <c r="J9" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" t="s">
-        <v>53</v>
       </c>
       <c r="M9" s="1">
         <v>2.8944600650390599</v>
@@ -1469,27 +1407,21 @@
         <v>6.289068541527107</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H10" s="2">
         <v>344</v>
@@ -1497,72 +1429,30 @@
       <c r="I10" s="2">
         <v>120</v>
       </c>
-      <c r="J10" s="11">
+      <c r="J10" s="2">
         <f t="shared" si="1"/>
         <v>0.34883720930232559</v>
       </c>
-      <c r="K10" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="M10" s="1"/>
       <c r="N10" s="1"/>
-      <c r="O10" t="s">
-        <v>53</v>
-      </c>
-      <c r="P10" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" t="s">
-        <v>53</v>
-      </c>
-      <c r="S10" t="s">
-        <v>53</v>
-      </c>
-      <c r="T10" t="s">
-        <v>53</v>
-      </c>
-      <c r="U10" t="s">
-        <v>53</v>
-      </c>
-      <c r="V10" t="s">
-        <v>53</v>
-      </c>
-      <c r="W10" t="s">
-        <v>53</v>
-      </c>
-      <c r="X10" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="W10"/>
+      <c r="X10"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" t="s">
-        <v>53</v>
-      </c>
-      <c r="D11" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H11" s="2">
         <v>490</v>
@@ -1570,18 +1460,9 @@
       <c r="I11" s="2">
         <v>294</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="2">
         <f t="shared" si="1"/>
         <v>0.6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" t="s">
-        <v>53</v>
       </c>
       <c r="O11">
         <v>84679.293103448275</v>
@@ -1620,27 +1501,21 @@
         <v>6.501585235470829</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C12" t="s">
-        <v>53</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H12" s="2">
         <v>258</v>
@@ -1648,71 +1523,31 @@
       <c r="I12" s="2">
         <v>71</v>
       </c>
-      <c r="J12" s="11">
+      <c r="J12" s="2">
         <f t="shared" si="1"/>
         <v>0.27519379844961239</v>
       </c>
-      <c r="K12" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" t="s">
-        <v>53</v>
-      </c>
       <c r="M12" s="1">
         <v>1.5588285248170117</v>
       </c>
-      <c r="O12" t="s">
-        <v>53</v>
-      </c>
-      <c r="P12" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" t="s">
-        <v>53</v>
-      </c>
-      <c r="S12" t="s">
-        <v>53</v>
-      </c>
-      <c r="T12" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" t="s">
-        <v>53</v>
-      </c>
-      <c r="V12" t="s">
-        <v>53</v>
-      </c>
-      <c r="W12" t="s">
-        <v>53</v>
-      </c>
-      <c r="X12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W12"/>
+      <c r="X12"/>
+    </row>
+    <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H13" s="2">
         <v>596</v>
@@ -1720,15 +1555,9 @@
       <c r="I13" s="2">
         <v>601</v>
       </c>
-      <c r="J13" s="11">
+      <c r="J13" s="2">
         <f t="shared" si="1"/>
         <v>1.0083892617449663</v>
-      </c>
-      <c r="K13" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" t="s">
-        <v>53</v>
       </c>
       <c r="M13" s="1">
         <v>2.7972467606932976</v>
@@ -1771,27 +1600,21 @@
         <v>6.3221347547058153</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" t="s">
         <v>60</v>
       </c>
-      <c r="B14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>71</v>
-      </c>
-      <c r="F14" t="s">
-        <v>62</v>
-      </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H14" s="2">
         <v>158</v>
@@ -1799,72 +1622,32 @@
       <c r="I14" s="2">
         <v>89</v>
       </c>
-      <c r="J14" s="11">
+      <c r="J14" s="2">
         <f t="shared" si="1"/>
         <v>0.56329113924050633</v>
       </c>
-      <c r="K14" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" t="s">
-        <v>53</v>
-      </c>
       <c r="M14" s="1">
         <v>1.4404367661057738</v>
       </c>
       <c r="N14" s="1"/>
-      <c r="O14" t="s">
-        <v>53</v>
-      </c>
-      <c r="P14" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>53</v>
-      </c>
-      <c r="R14" t="s">
-        <v>53</v>
-      </c>
-      <c r="S14" t="s">
-        <v>53</v>
-      </c>
-      <c r="T14" t="s">
-        <v>53</v>
-      </c>
-      <c r="U14" t="s">
-        <v>53</v>
-      </c>
-      <c r="V14" t="s">
-        <v>53</v>
-      </c>
-      <c r="W14" t="s">
-        <v>53</v>
-      </c>
-      <c r="X14" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W14"/>
+      <c r="X14"/>
+    </row>
+    <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G15" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H15" s="2">
         <v>317</v>
@@ -1872,15 +1655,9 @@
       <c r="I15" s="2">
         <v>323</v>
       </c>
-      <c r="J15" s="11">
+      <c r="J15" s="2">
         <f t="shared" si="1"/>
         <v>1.0189274447949528</v>
-      </c>
-      <c r="K15" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" t="s">
-        <v>53</v>
       </c>
       <c r="M15">
         <v>3.1017745600690869</v>
@@ -1923,27 +1700,21 @@
         <v>6.2737680984010069</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2">
         <v>108</v>
@@ -1951,72 +1722,32 @@
       <c r="I16" s="2">
         <v>61</v>
       </c>
-      <c r="J16" s="11">
+      <c r="J16" s="2">
         <f t="shared" si="1"/>
         <v>0.56481481481481477</v>
       </c>
-      <c r="K16" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" t="s">
-        <v>53</v>
-      </c>
       <c r="M16">
         <v>1.2986347831244356</v>
       </c>
       <c r="N16" s="1"/>
-      <c r="O16" t="s">
-        <v>53</v>
-      </c>
-      <c r="P16" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" t="s">
-        <v>53</v>
-      </c>
-      <c r="S16" t="s">
-        <v>53</v>
-      </c>
-      <c r="T16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" t="s">
-        <v>53</v>
-      </c>
-      <c r="V16" t="s">
-        <v>53</v>
-      </c>
-      <c r="W16" t="s">
-        <v>53</v>
-      </c>
-      <c r="X16" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W16"/>
+      <c r="X16"/>
+    </row>
+    <row r="17" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H17" s="2">
         <v>507</v>
@@ -2024,15 +1755,9 @@
       <c r="I17" s="2">
         <v>314</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="2">
         <f t="shared" si="1"/>
         <v>0.61932938856015785</v>
-      </c>
-      <c r="K17" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" t="s">
-        <v>53</v>
       </c>
       <c r="M17" s="1">
         <v>2.7742906356888972</v>
@@ -2075,27 +1800,27 @@
         <v>6.5083866073242458</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" t="s">
         <v>38</v>
       </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>39</v>
-      </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H18" s="2">
         <v>496</v>
@@ -2103,7 +1828,7 @@
       <c r="I18" s="2">
         <v>264</v>
       </c>
-      <c r="J18" s="11">
+      <c r="J18" s="2">
         <f t="shared" si="1"/>
         <v>0.532258064516129</v>
       </c>
@@ -2154,27 +1879,27 @@
         <v>6.4359653564343713</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H19" s="2">
         <v>0</v>
@@ -2182,7 +1907,7 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="11">
+      <c r="J19" s="2">
         <v>0</v>
       </c>
       <c r="K19">
@@ -2232,27 +1957,21 @@
         <v>6.5817565316623368</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E20" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2">
         <v>511</v>
@@ -2260,72 +1979,32 @@
       <c r="I20" s="2">
         <v>541</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="2">
         <f t="shared" si="1"/>
         <v>1.0587084148727985</v>
       </c>
-      <c r="K20" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" t="s">
-        <v>53</v>
-      </c>
       <c r="M20">
         <v>1.6893088591236203</v>
       </c>
       <c r="N20" s="1"/>
-      <c r="O20" t="s">
-        <v>53</v>
-      </c>
-      <c r="P20" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>53</v>
-      </c>
-      <c r="R20" t="s">
-        <v>53</v>
-      </c>
-      <c r="S20" t="s">
-        <v>53</v>
-      </c>
-      <c r="T20" t="s">
-        <v>53</v>
-      </c>
-      <c r="U20" t="s">
-        <v>53</v>
-      </c>
-      <c r="V20" t="s">
-        <v>53</v>
-      </c>
-      <c r="W20" t="s">
-        <v>53</v>
-      </c>
-      <c r="X20" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W20"/>
+      <c r="X20"/>
+    </row>
+    <row r="21" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="H21" s="2">
         <v>574</v>
@@ -2333,15 +2012,9 @@
       <c r="I21" s="2">
         <v>86</v>
       </c>
-      <c r="J21" s="11">
+      <c r="J21" s="2">
         <f t="shared" si="1"/>
         <v>0.14982578397212543</v>
-      </c>
-      <c r="K21" t="s">
-        <v>53</v>
-      </c>
-      <c r="L21" t="s">
-        <v>53</v>
       </c>
       <c r="M21">
         <v>2.5814376192313899</v>
@@ -2384,27 +2057,27 @@
         <v>5.9155398021589978</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="5" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="H22" s="6">
         <v>318</v>
@@ -2462,27 +2135,27 @@
         <v>6.8226041131618205</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2">
         <v>531</v>
@@ -2490,7 +2163,7 @@
       <c r="I23" s="2">
         <v>539</v>
       </c>
-      <c r="J23" s="11">
+      <c r="J23" s="2">
         <f t="shared" si="1"/>
         <v>1.0150659133709981</v>
       </c>
@@ -2541,27 +2214,27 @@
         <v>6.3465105295155722</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E24" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H24" s="2">
         <v>573</v>
@@ -2569,7 +2242,7 @@
       <c r="I24" s="2">
         <v>344</v>
       </c>
-      <c r="J24" s="11">
+      <c r="J24" s="2">
         <f t="shared" si="1"/>
         <v>0.6003490401396161</v>
       </c>
@@ -2620,27 +2293,27 @@
         <v>6.7765911018548994</v>
       </c>
     </row>
-    <row r="25" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F25" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H25" s="2">
         <v>508</v>
@@ -2648,7 +2321,7 @@
       <c r="I25" s="2">
         <v>539</v>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="2">
         <f t="shared" si="1"/>
         <v>1.061023622047244</v>
       </c>
@@ -2699,27 +2372,27 @@
         <v>6.4833593470932165</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E26" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H26" s="2">
         <v>381</v>
@@ -2727,7 +2400,7 @@
       <c r="I26" s="2">
         <v>101</v>
       </c>
-      <c r="J26" s="11">
+      <c r="J26" s="2">
         <f t="shared" si="1"/>
         <v>0.26509186351706038</v>
       </c>
@@ -2778,27 +2451,27 @@
         <v>6.3107381622693346</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H27" s="2">
         <v>0</v>
@@ -2806,7 +2479,7 @@
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="11">
+      <c r="J27" s="2">
         <v>0</v>
       </c>
       <c r="K27">
@@ -2856,27 +2529,27 @@
         <v>6.0521405858199371</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E28" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" s="2">
         <v>45</v>
@@ -2884,7 +2557,7 @@
       <c r="I28" s="2">
         <v>24</v>
       </c>
-      <c r="J28" s="11">
+      <c r="J28" s="2">
         <f t="shared" si="1"/>
         <v>0.53333333333333333</v>
       </c>
@@ -2898,58 +2571,30 @@
         <v>2.0773315611289904</v>
       </c>
       <c r="N28" s="1"/>
-      <c r="O28" t="s">
-        <v>53</v>
-      </c>
-      <c r="P28" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>53</v>
-      </c>
-      <c r="R28" t="s">
-        <v>53</v>
-      </c>
-      <c r="S28" t="s">
-        <v>53</v>
-      </c>
-      <c r="T28" t="s">
-        <v>53</v>
-      </c>
-      <c r="U28" t="s">
-        <v>53</v>
-      </c>
-      <c r="V28" t="s">
-        <v>53</v>
-      </c>
-      <c r="W28" t="s">
-        <v>53</v>
-      </c>
-      <c r="X28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="W28"/>
+      <c r="X28"/>
+    </row>
+    <row r="29" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D29" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H29" s="2">
         <v>480</v>
@@ -2957,7 +2602,7 @@
       <c r="I29" s="2">
         <v>266</v>
       </c>
-      <c r="J29" s="11">
+      <c r="J29" s="2">
         <f t="shared" si="1"/>
         <v>0.5541666666666667</v>
       </c>
@@ -3008,27 +2653,27 @@
         <v>6.4431933936618071</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H30" s="2">
         <v>468</v>
@@ -3036,7 +2681,7 @@
       <c r="I30" s="2">
         <v>565</v>
       </c>
-      <c r="J30" s="11">
+      <c r="J30" s="2">
         <f t="shared" si="1"/>
         <v>1.2072649572649572</v>
       </c>
@@ -3087,27 +2732,27 @@
         <v>6.4579598324703573</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B31" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H31" s="2">
         <v>274</v>
@@ -3115,7 +2760,7 @@
       <c r="I31" s="2">
         <v>0</v>
       </c>
-      <c r="J31" s="11">
+      <c r="J31" s="2">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -3166,27 +2811,27 @@
         <v>6.072972328273023</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="H32" s="2">
         <v>582</v>
@@ -3194,7 +2839,7 @@
       <c r="I32" s="2">
         <v>125</v>
       </c>
-      <c r="J32" s="11">
+      <c r="J32" s="2">
         <f t="shared" si="1"/>
         <v>0.21477663230240548</v>
       </c>
@@ -3245,27 +2890,27 @@
         <v>6.8143334206600334</v>
       </c>
     </row>
-    <row r="33" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E33" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F33" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>76</v>
+        <v>99</v>
       </c>
       <c r="H33" s="2">
         <v>590</v>
@@ -3273,7 +2918,7 @@
       <c r="I33" s="2">
         <v>152</v>
       </c>
-      <c r="J33" s="11">
+      <c r="J33" s="2">
         <f t="shared" si="1"/>
         <v>0.25762711864406779</v>
       </c>

--- a/Reference/Complete Data Frame (Hormones, Behavior, Size, Gonads) GG.xlsx
+++ b/Reference/Complete Data Frame (Hormones, Behavior, Size, Gonads) GG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10329"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ggraham/Desktop/multiome_poa/Reference/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/jrhodes/Fish Lab/Experiments/sex change single nuc POA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49EA4129-8D06-284B-A7C0-1E946C8336E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01E83780-B185-D04A-8B36-5EEF67667FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="100" yWindow="780" windowWidth="27000" windowHeight="14260" xr2:uid="{4C85D3C2-4423-4DD6-A968-B296FD30C807}"/>
   </bookViews>
@@ -317,16 +317,10 @@
     <t>Log10_Testicular_Estimate</t>
   </si>
   <si>
-    <t>Percent_Ovarian</t>
-  </si>
-  <si>
-    <t>Ovarian_Estimate</t>
-  </si>
-  <si>
-    <t>Log10_Ovarian_Estimate</t>
-  </si>
-  <si>
-    <t>Behaviors_Per_Time</t>
+    <t>length_init_cm</t>
+  </si>
+  <si>
+    <t>mass_init_g</t>
   </si>
   <si>
     <t>Total_Slides_With_God</t>
@@ -336,15 +330,28 @@
   </si>
   <si>
     <t>Subordite</t>
+  </si>
+  <si>
+    <t>length_final_cm</t>
+  </si>
+  <si>
+    <t>mass_final_cm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -365,8 +372,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -392,7 +400,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -400,39 +408,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -757,7 +744,7 @@
     <col min="11" max="12" width="9.1640625"/>
     <col min="15" max="15" width="13.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="24.1640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="8.83203125" style="10"/>
+    <col min="23" max="24" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
@@ -789,127 +776,121 @@
         <v>64</v>
       </c>
       <c r="J1" t="s">
-        <v>96</v>
+        <v>65</v>
       </c>
       <c r="K1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="M1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N1" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="O1" t="s">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="P1" t="s">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="Q1" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="R1" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="S1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="T1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="V1" t="s">
-        <v>93</v>
-      </c>
-      <c r="W1" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="X1" s="10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="W1" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="X1" s="3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" t="s">
         <v>80</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>68</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2">
         <v>274</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2">
         <v>68</v>
       </c>
-      <c r="J2" s="6">
-        <f>I2/H2</f>
-        <v>0.24817518248175183</v>
-      </c>
-      <c r="K2" s="5">
-        <v>112.72727272727272</v>
-      </c>
-      <c r="L2" s="7">
+      <c r="J2">
+        <v>112.7273</v>
+      </c>
+      <c r="K2">
         <v>147.1429</v>
       </c>
-      <c r="M2" s="8">
-        <v>1.53932706</v>
-      </c>
-      <c r="N2" s="9"/>
-      <c r="O2" s="5">
-        <v>162318.61363636365</v>
-      </c>
-      <c r="P2" s="5">
+      <c r="L2" s="4">
+        <v>1.5393269999999999</v>
+      </c>
+      <c r="M2" s="4"/>
+      <c r="N2">
+        <v>162318.61360000001</v>
+      </c>
+      <c r="O2">
         <v>87</v>
       </c>
-      <c r="Q2" s="5">
-        <f t="shared" ref="Q2:Q7" si="0">O2*P2</f>
-        <v>14121719.386363637</v>
-      </c>
-      <c r="R2" s="5">
-        <f>LOG10(Q2)</f>
-        <v>7.1498875773496229</v>
-      </c>
-      <c r="S2" s="5">
+      <c r="P2">
+        <v>14121719</v>
+      </c>
+      <c r="Q2">
+        <v>7.1498879999999998</v>
+      </c>
+      <c r="R2">
         <v>0</v>
       </c>
-      <c r="T2" s="5">
-        <f>(S2*Q2)</f>
+      <c r="S2">
         <v>0</v>
       </c>
-      <c r="U2" s="5">
+      <c r="T2">
         <v>0</v>
       </c>
-      <c r="V2" s="5">
-        <v>0.44462482068665182</v>
-      </c>
-      <c r="W2" s="5">
-        <f>V2*Q2</f>
-        <v>6278866.9499491472</v>
-      </c>
-      <c r="X2" s="5">
-        <f>LOG10(W2)</f>
-        <v>6.7978812803962834</v>
+      <c r="U2">
+        <v>5.5</v>
+      </c>
+      <c r="V2">
+        <v>3.5</v>
+      </c>
+      <c r="W2">
+        <v>6.2</v>
+      </c>
+      <c r="X2">
+        <v>5.15</v>
       </c>
     </row>
     <row r="3" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -934,61 +915,54 @@
       <c r="G3" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3">
         <v>557</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3">
         <v>546</v>
       </c>
-      <c r="J3" s="2">
-        <f t="shared" ref="J3:J33" si="1">I3/H3</f>
-        <v>0.98025134649910228</v>
+      <c r="J3">
+        <v>102.08329999999999</v>
       </c>
       <c r="K3">
-        <v>102.08333333333334</v>
+        <v>98.139529999999993</v>
       </c>
       <c r="L3" s="4">
-        <v>98.139529999999993</v>
-      </c>
-      <c r="M3" s="1">
-        <v>2.6314234744043268</v>
-      </c>
-      <c r="N3" s="1"/>
+        <v>2.6314229999999998</v>
+      </c>
+      <c r="M3" s="4"/>
+      <c r="N3">
+        <v>45782.466670000002</v>
+      </c>
       <c r="O3">
-        <v>45782.466666666667</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>61</v>
+        <v>2792730</v>
       </c>
       <c r="Q3">
-        <f t="shared" si="0"/>
-        <v>2792730.4666666668</v>
-      </c>
-      <c r="R3" s="10">
-        <f t="shared" ref="R3:R33" si="2">LOG10(Q3)</f>
-        <v>6.4460290228875801</v>
+        <v>6.4460290000000002</v>
+      </c>
+      <c r="R3">
+        <v>0.372693</v>
       </c>
       <c r="S3">
-        <v>0.37269314003123571</v>
-      </c>
-      <c r="T3" s="10">
-        <f t="shared" ref="T3:T33" si="3">(S3*Q3)</f>
-        <v>1040831.4868828983</v>
-      </c>
-      <c r="U3" s="10">
-        <f t="shared" ref="U3:U33" si="4">LOG10(T3)</f>
-        <v>6.0173804218823665</v>
+        <v>1040831</v>
+      </c>
+      <c r="T3">
+        <v>6.0173800000000002</v>
+      </c>
+      <c r="U3">
+        <v>4.8</v>
       </c>
       <c r="V3">
-        <v>0.57920315529777588</v>
-      </c>
-      <c r="W3" s="10">
-        <f t="shared" ref="W3:W33" si="5">V3*Q3</f>
-        <v>1617558.2981895634</v>
-      </c>
-      <c r="X3" s="10">
-        <f t="shared" ref="X3:X33" si="6">LOG10(W3)</f>
-        <v>6.2088599419687291</v>
+        <v>2.15</v>
+      </c>
+      <c r="W3">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X3">
+        <v>2.11</v>
       </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.2">
@@ -1011,63 +985,55 @@
         <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H4" s="2">
+        <v>96</v>
+      </c>
+      <c r="H4">
         <v>274</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4">
         <v>746</v>
       </c>
-      <c r="J4" s="2">
-        <f t="shared" si="1"/>
-        <v>2.7226277372262775</v>
+      <c r="J4">
+        <v>108.33329999999999</v>
       </c>
       <c r="K4">
-        <v>108.33333333333333</v>
-      </c>
-      <c r="L4" s="4">
         <v>131.38890000000001</v>
       </c>
-      <c r="M4" s="2">
-        <v>3.1245335680647184</v>
-      </c>
-      <c r="N4" s="2"/>
+      <c r="L4">
+        <v>3.1245340000000001</v>
+      </c>
+      <c r="N4">
+        <v>63569.204550000002</v>
+      </c>
       <c r="O4">
-        <v>63569.204545454544</v>
+        <v>89</v>
       </c>
       <c r="P4">
-        <v>89</v>
+        <v>5657659</v>
       </c>
       <c r="Q4">
-        <f t="shared" si="0"/>
-        <v>5657659.2045454541</v>
-      </c>
-      <c r="R4" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7526367836930969</v>
+        <v>6.752637</v>
+      </c>
+      <c r="R4">
+        <v>0.24757699999999999</v>
       </c>
       <c r="S4">
-        <v>0.24757687395297898</v>
-      </c>
-      <c r="T4" s="10">
-        <f t="shared" si="3"/>
-        <v>1400705.5797526613</v>
-      </c>
-      <c r="U4" s="10">
-        <f t="shared" si="4"/>
-        <v>6.1463468586790002</v>
+        <v>1400706</v>
+      </c>
+      <c r="T4">
+        <v>6.1463469999999996</v>
+      </c>
+      <c r="U4">
+        <v>6</v>
       </c>
       <c r="V4">
-        <v>0.6754977121785809</v>
-      </c>
-      <c r="W4" s="10">
-        <f t="shared" si="5"/>
-        <v>3821735.848956544</v>
-      </c>
-      <c r="X4" s="10">
-        <f t="shared" si="6"/>
-        <v>6.5822606661556602</v>
+        <v>3.6</v>
+      </c>
+      <c r="W4">
+        <v>6.5</v>
+      </c>
+      <c r="X4">
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1090,63 +1056,56 @@
         <v>28</v>
       </c>
       <c r="G5" t="s">
-        <v>99</v>
-      </c>
-      <c r="H5" s="2">
+        <v>97</v>
+      </c>
+      <c r="H5">
         <v>24</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5">
         <v>2</v>
       </c>
-      <c r="J5" s="2">
-        <f t="shared" si="1"/>
-        <v>8.3333333333333329E-2</v>
+      <c r="J5">
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>97.609560000000002</v>
       </c>
       <c r="L5" s="4">
-        <v>97.609560000000002</v>
-      </c>
-      <c r="M5" s="1">
-        <v>2.0785293152543463</v>
-      </c>
-      <c r="N5" s="1"/>
+        <v>2.0785290000000001</v>
+      </c>
+      <c r="M5" s="4"/>
+      <c r="N5">
+        <v>30791.769230000002</v>
+      </c>
       <c r="O5">
-        <v>30791.76923076923</v>
+        <v>31</v>
       </c>
       <c r="P5">
-        <v>31</v>
+        <v>954544.8</v>
       </c>
       <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>954544.84615384613</v>
-      </c>
-      <c r="R5" s="10">
-        <f t="shared" si="2"/>
-        <v>5.9797963371085485</v>
+        <v>5.9797960000000003</v>
+      </c>
+      <c r="R5">
+        <v>5.9414000000000002E-2</v>
       </c>
       <c r="S5">
-        <v>5.9414442892181583E-2</v>
-      </c>
-      <c r="T5" s="10">
-        <f t="shared" si="3"/>
-        <v>56713.750249833945</v>
-      </c>
-      <c r="U5" s="10">
-        <f t="shared" si="4"/>
-        <v>4.7536883663647744</v>
+        <v>56713.75</v>
+      </c>
+      <c r="T5">
+        <v>4.7536880000000004</v>
+      </c>
+      <c r="U5">
+        <v>5.2</v>
       </c>
       <c r="V5">
-        <v>0.88161006162864575</v>
-      </c>
-      <c r="W5" s="10">
-        <f t="shared" si="5"/>
-        <v>841536.34064499848</v>
-      </c>
-      <c r="X5" s="10">
-        <f t="shared" si="6"/>
-        <v>5.925072875155351</v>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="W5">
+        <v>5.2</v>
+      </c>
+      <c r="X5">
+        <v>2.4500000000000002</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
@@ -1169,63 +1128,55 @@
         <v>27</v>
       </c>
       <c r="G6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="2">
+        <v>96</v>
+      </c>
+      <c r="H6">
         <v>571</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6">
         <v>543</v>
       </c>
-      <c r="J6" s="2">
-        <f t="shared" si="1"/>
-        <v>0.95096322241681264</v>
+      <c r="J6">
+        <v>110.1695</v>
       </c>
       <c r="K6">
-        <v>110.16949152542372</v>
-      </c>
-      <c r="L6" s="4">
         <v>148.8827</v>
       </c>
-      <c r="M6" s="2">
-        <v>2.4731949092049379</v>
-      </c>
-      <c r="N6" s="2"/>
+      <c r="L6">
+        <v>2.473195</v>
+      </c>
+      <c r="N6">
+        <v>69189.027780000004</v>
+      </c>
       <c r="O6">
-        <v>69189.027777777781</v>
+        <v>74</v>
       </c>
       <c r="P6">
-        <v>74</v>
+        <v>5119988</v>
       </c>
       <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>5119988.055555556</v>
-      </c>
-      <c r="R6" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7092689478093535</v>
+        <v>6.7092689999999999</v>
+      </c>
+      <c r="R6">
+        <v>0.20338899999999999</v>
       </c>
       <c r="S6">
-        <v>0.20338877118702384</v>
-      </c>
-      <c r="T6" s="10">
-        <f t="shared" si="3"/>
-        <v>1041348.0791116841</v>
-      </c>
-      <c r="U6" s="10">
-        <f t="shared" si="4"/>
-        <v>6.0175959202597626</v>
+        <v>1041348</v>
+      </c>
+      <c r="T6">
+        <v>6.0175960000000002</v>
+      </c>
+      <c r="U6">
+        <v>5.9</v>
       </c>
       <c r="V6">
-        <v>0.68365429952970025</v>
-      </c>
-      <c r="W6" s="10">
-        <f t="shared" si="5"/>
-        <v>3500301.8477212656</v>
-      </c>
-      <c r="X6" s="10">
-        <f t="shared" si="6"/>
-        <v>6.5441054972494941</v>
+        <v>3.58</v>
+      </c>
+      <c r="W6">
+        <v>6.5</v>
+      </c>
+      <c r="X6">
+        <v>5.33</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1248,63 +1199,56 @@
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>99</v>
-      </c>
-      <c r="H7" s="2">
+        <v>97</v>
+      </c>
+      <c r="H7">
         <v>162</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="J7">
+        <v>102.08329999999999</v>
       </c>
       <c r="K7">
-        <v>102.08333333333334</v>
+        <v>93.181820000000002</v>
       </c>
       <c r="L7" s="4">
-        <v>93.181820000000002</v>
-      </c>
-      <c r="M7" s="1">
-        <v>2.3331852080527624</v>
-      </c>
-      <c r="N7" s="1"/>
+        <v>2.3331849999999998</v>
+      </c>
+      <c r="M7" s="4"/>
+      <c r="N7">
+        <v>37532.631580000001</v>
+      </c>
       <c r="O7">
-        <v>37532.631578947367</v>
+        <v>40</v>
       </c>
       <c r="P7">
-        <v>40</v>
+        <v>1501305</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="0"/>
-        <v>1501305.2631578946</v>
-      </c>
-      <c r="R7" s="10">
-        <f t="shared" si="2"/>
-        <v>6.1764690071172348</v>
+        <v>6.176469</v>
+      </c>
+      <c r="R7">
+        <v>0.12797600000000001</v>
       </c>
       <c r="S7">
-        <v>0.1279758425741023</v>
-      </c>
-      <c r="T7" s="10">
-        <f t="shared" si="3"/>
-        <v>192130.80601356595</v>
-      </c>
-      <c r="U7" s="10">
-        <f t="shared" si="4"/>
-        <v>5.2835970046798471</v>
+        <v>192130.8</v>
+      </c>
+      <c r="T7">
+        <v>5.2835970000000003</v>
+      </c>
+      <c r="U7">
+        <v>4.8</v>
       </c>
       <c r="V7">
-        <v>0.77804639082387717</v>
-      </c>
-      <c r="W7" s="10">
-        <f t="shared" si="5"/>
-        <v>1168085.1415248909</v>
-      </c>
-      <c r="X7" s="10">
-        <f t="shared" si="6"/>
-        <v>6.0674744995801504</v>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="W7">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="X7">
+        <v>2.0499999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1323,22 +1267,28 @@
       <c r="G8" t="s">
         <v>73</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8">
         <v>449</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8">
         <v>120</v>
       </c>
-      <c r="J8" s="2">
-        <f t="shared" si="1"/>
-        <v>0.267260579064588</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1.669967369908504</v>
-      </c>
-      <c r="N8" s="1"/>
-      <c r="W8"/>
-      <c r="X8"/>
+      <c r="L8" s="4">
+        <v>1.669967</v>
+      </c>
+      <c r="M8" s="4"/>
+      <c r="S8" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T8" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W8">
+        <v>7.9</v>
+      </c>
+      <c r="X8">
+        <v>10.61</v>
+      </c>
     </row>
     <row r="9" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -1356,55 +1306,42 @@
       <c r="G9" t="s">
         <v>74</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9">
         <v>600</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9">
         <v>600</v>
       </c>
-      <c r="J9" s="2">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="1">
-        <v>2.8944600650390599</v>
-      </c>
-      <c r="N9" s="1"/>
+      <c r="L9" s="4">
+        <v>2.89446</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9">
+        <v>105617.05</v>
+      </c>
       <c r="O9">
-        <v>105617.05</v>
+        <v>81</v>
       </c>
       <c r="P9">
-        <v>81</v>
+        <v>8554981</v>
       </c>
       <c r="Q9">
-        <f>O9*P9</f>
-        <v>8554981.0500000007</v>
-      </c>
-      <c r="R9" s="10">
-        <f t="shared" si="2"/>
-        <v>6.9322190518795095</v>
+        <v>6.9322189999999999</v>
+      </c>
+      <c r="R9">
+        <v>0.70937700000000004</v>
       </c>
       <c r="S9">
-        <v>0.70937709964454521</v>
-      </c>
-      <c r="T9" s="10">
-        <f t="shared" si="3"/>
-        <v>6068707.6447630469</v>
-      </c>
-      <c r="U9" s="10">
-        <f t="shared" si="4"/>
-        <v>6.7830962161979294</v>
-      </c>
-      <c r="V9">
-        <v>0.22743091030332827</v>
-      </c>
-      <c r="W9" s="10">
-        <f t="shared" si="5"/>
-        <v>1945667.1278292232</v>
-      </c>
-      <c r="X9" s="10">
-        <f t="shared" si="6"/>
-        <v>6.289068541527107</v>
+        <v>6068708</v>
+      </c>
+      <c r="T9">
+        <v>6.7830959999999996</v>
+      </c>
+      <c r="W9">
+        <v>5</v>
+      </c>
+      <c r="X9">
+        <v>2.4900000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1423,20 +1360,26 @@
       <c r="G10" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10">
         <v>344</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10">
         <v>120</v>
       </c>
-      <c r="J10" s="2">
-        <f t="shared" si="1"/>
-        <v>0.34883720930232559</v>
-      </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="W10"/>
-      <c r="X10"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="S10" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T10" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W10">
+        <v>7.9</v>
+      </c>
+      <c r="X10">
+        <v>10.07</v>
+      </c>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -1454,51 +1397,38 @@
       <c r="G11" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11">
         <v>490</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11">
         <v>294</v>
       </c>
-      <c r="J11" s="2">
-        <f t="shared" si="1"/>
-        <v>0.6</v>
+      <c r="N11">
+        <v>84679.293099999995</v>
       </c>
       <c r="O11">
-        <v>84679.293103448275</v>
+        <v>119</v>
       </c>
       <c r="P11">
-        <v>119</v>
+        <v>10076836</v>
       </c>
       <c r="Q11">
-        <f>O11*P11</f>
-        <v>10076835.879310345</v>
-      </c>
-      <c r="R11" s="10">
-        <f t="shared" si="2"/>
-        <v>7.0033241852964343</v>
+        <v>7.0033240000000001</v>
+      </c>
+      <c r="R11">
+        <v>0.62347799999999998</v>
       </c>
       <c r="S11">
-        <v>0.6234779064944328</v>
-      </c>
-      <c r="T11" s="10">
-        <f t="shared" si="3"/>
-        <v>6282684.5381204011</v>
-      </c>
-      <c r="U11" s="10">
-        <f t="shared" si="4"/>
-        <v>6.7981452537644733</v>
-      </c>
-      <c r="V11">
-        <v>0.31496409636607697</v>
-      </c>
-      <c r="W11" s="10">
-        <f t="shared" si="5"/>
-        <v>3173841.5069562458</v>
-      </c>
-      <c r="X11" s="10">
-        <f t="shared" si="6"/>
-        <v>6.501585235470829</v>
+        <v>6282685</v>
+      </c>
+      <c r="T11">
+        <v>6.7981449999999999</v>
+      </c>
+      <c r="W11">
+        <v>6.4</v>
+      </c>
+      <c r="X11">
+        <v>4.7300000000000004</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1517,21 +1447,27 @@
       <c r="G12" t="s">
         <v>73</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12">
         <v>258</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12">
         <v>71</v>
       </c>
-      <c r="J12" s="2">
-        <f t="shared" si="1"/>
-        <v>0.27519379844961239</v>
-      </c>
-      <c r="M12" s="1">
-        <v>1.5588285248170117</v>
-      </c>
-      <c r="W12"/>
-      <c r="X12"/>
+      <c r="L12" s="4">
+        <v>1.558829</v>
+      </c>
+      <c r="S12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T12" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W12">
+        <v>7.4</v>
+      </c>
+      <c r="X12">
+        <v>8.7100000000000009</v>
+      </c>
     </row>
     <row r="13" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -1549,55 +1485,42 @@
       <c r="G13" t="s">
         <v>74</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>596</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13">
         <v>601</v>
       </c>
-      <c r="J13" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0083892617449663</v>
-      </c>
-      <c r="M13" s="1">
-        <v>2.7972467606932976</v>
-      </c>
-      <c r="N13" s="1"/>
+      <c r="L13" s="4">
+        <v>2.797247</v>
+      </c>
+      <c r="M13" s="4"/>
+      <c r="N13">
+        <v>130529.39290000001</v>
+      </c>
       <c r="O13">
-        <v>130529.39285714286</v>
+        <v>58</v>
       </c>
       <c r="P13">
-        <v>58</v>
+        <v>7570705</v>
       </c>
       <c r="Q13">
-        <f>O13*P13</f>
-        <v>7570704.7857142854</v>
-      </c>
-      <c r="R13" s="10">
-        <f t="shared" si="2"/>
-        <v>6.879136311507855</v>
+        <v>6.8791359999999999</v>
+      </c>
+      <c r="R13">
+        <v>0.67587799999999998</v>
       </c>
       <c r="S13">
-        <v>0.67587777091082946</v>
-      </c>
-      <c r="T13" s="10">
-        <f t="shared" si="3"/>
-        <v>5116871.0747925201</v>
-      </c>
-      <c r="U13" s="10">
-        <f t="shared" si="4"/>
-        <v>6.7090044745817394</v>
-      </c>
-      <c r="V13">
-        <v>0.27733101632345847</v>
-      </c>
-      <c r="W13" s="10">
-        <f t="shared" si="5"/>
-        <v>2099591.2525070137</v>
-      </c>
-      <c r="X13" s="10">
-        <f t="shared" si="6"/>
-        <v>6.3221347547058153</v>
+        <v>5116871</v>
+      </c>
+      <c r="T13">
+        <v>6.7090040000000002</v>
+      </c>
+      <c r="W13">
+        <v>5.3</v>
+      </c>
+      <c r="X13">
+        <v>2.74</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1616,22 +1539,28 @@
       <c r="G14" t="s">
         <v>73</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14">
         <v>158</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14">
         <v>89</v>
       </c>
-      <c r="J14" s="2">
-        <f t="shared" si="1"/>
-        <v>0.56329113924050633</v>
-      </c>
-      <c r="M14" s="1">
-        <v>1.4404367661057738</v>
-      </c>
-      <c r="N14" s="1"/>
-      <c r="W14"/>
-      <c r="X14"/>
+      <c r="L14" s="4">
+        <v>1.440437</v>
+      </c>
+      <c r="M14" s="4"/>
+      <c r="S14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T14" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W14">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="X14">
+        <v>14.24</v>
+      </c>
     </row>
     <row r="15" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -1649,55 +1578,42 @@
       <c r="G15" t="s">
         <v>74</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15">
         <v>317</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15">
         <v>323</v>
       </c>
-      <c r="J15" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0189274447949528</v>
-      </c>
-      <c r="M15">
-        <v>3.1017745600690869</v>
-      </c>
-      <c r="N15" s="1"/>
+      <c r="L15">
+        <v>3.1017749999999999</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15">
+        <v>73653.444440000007</v>
+      </c>
       <c r="O15">
-        <v>73653.444444444438</v>
+        <v>92</v>
       </c>
       <c r="P15">
-        <v>92</v>
+        <v>6776117</v>
       </c>
       <c r="Q15">
-        <f>O15*P15</f>
-        <v>6776116.8888888881</v>
-      </c>
-      <c r="R15" s="10">
-        <f t="shared" si="2"/>
-        <v>6.8309808890230039</v>
+        <v>6.8309810000000004</v>
+      </c>
+      <c r="R15">
+        <v>0.67927300000000002</v>
       </c>
       <c r="S15">
-        <v>0.67927268660216078</v>
-      </c>
-      <c r="T15" s="10">
-        <f t="shared" si="3"/>
-        <v>4602831.1238458306</v>
-      </c>
-      <c r="U15" s="10">
-        <f t="shared" si="4"/>
-        <v>6.6630250410840004</v>
-      </c>
-      <c r="V15">
-        <v>0.27719615979608658</v>
-      </c>
-      <c r="W15" s="10">
-        <f t="shared" si="5"/>
-        <v>1878313.5799294054</v>
-      </c>
-      <c r="X15" s="10">
-        <f t="shared" si="6"/>
-        <v>6.2737680984010069</v>
+        <v>4602831</v>
+      </c>
+      <c r="T15">
+        <v>6.6630250000000002</v>
+      </c>
+      <c r="W15">
+        <v>5.9</v>
+      </c>
+      <c r="X15">
+        <v>4.12</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1716,22 +1632,28 @@
       <c r="G16" t="s">
         <v>73</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>108</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16">
         <v>61</v>
       </c>
-      <c r="J16" s="2">
-        <f t="shared" si="1"/>
-        <v>0.56481481481481477</v>
-      </c>
-      <c r="M16">
-        <v>1.2986347831244356</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="W16"/>
-      <c r="X16"/>
+      <c r="L16">
+        <v>1.298635</v>
+      </c>
+      <c r="M16" s="4"/>
+      <c r="S16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T16" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W16">
+        <v>7.9</v>
+      </c>
+      <c r="X16">
+        <v>9.44</v>
+      </c>
     </row>
     <row r="17" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -1749,55 +1671,42 @@
       <c r="G17" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17">
         <v>507</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17">
         <v>314</v>
       </c>
-      <c r="J17" s="2">
-        <f t="shared" si="1"/>
-        <v>0.61932938856015785</v>
-      </c>
-      <c r="M17" s="1">
-        <v>2.7742906356888972</v>
-      </c>
-      <c r="N17" s="1"/>
+      <c r="L17" s="4">
+        <v>2.7742909999999998</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17">
+        <v>128125.8919</v>
+      </c>
       <c r="O17">
-        <v>128125.89189189189</v>
+        <v>74</v>
       </c>
       <c r="P17">
-        <v>74</v>
+        <v>9481316</v>
       </c>
       <c r="Q17">
-        <f>O17*P17</f>
-        <v>9481316</v>
-      </c>
-      <c r="R17" s="10">
-        <f t="shared" si="2"/>
-        <v>6.9768686212908362</v>
+        <v>6.9768689999999998</v>
+      </c>
+      <c r="R17">
+        <v>0.60376799999999997</v>
       </c>
       <c r="S17">
-        <v>0.60376788312760132</v>
-      </c>
-      <c r="T17" s="10">
-        <f t="shared" si="3"/>
-        <v>5724514.0905838562</v>
-      </c>
-      <c r="U17" s="10">
-        <f t="shared" si="4"/>
-        <v>6.7577386287002863</v>
-      </c>
-      <c r="V17">
-        <v>0.34003058766586181</v>
-      </c>
-      <c r="W17" s="10">
-        <f t="shared" si="5"/>
-        <v>3223937.4513257383</v>
-      </c>
-      <c r="X17" s="10">
-        <f t="shared" si="6"/>
-        <v>6.5083866073242458</v>
+        <v>5724514</v>
+      </c>
+      <c r="T17">
+        <v>6.7577389999999999</v>
+      </c>
+      <c r="W17">
+        <v>5.4</v>
+      </c>
+      <c r="X17">
+        <v>3.07</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1820,63 +1729,56 @@
         <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>98</v>
-      </c>
-      <c r="H18" s="2">
+        <v>96</v>
+      </c>
+      <c r="H18">
         <v>496</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18">
         <v>264</v>
       </c>
-      <c r="J18" s="2">
-        <f t="shared" si="1"/>
-        <v>0.532258064516129</v>
+      <c r="J18">
+        <v>109.2308</v>
       </c>
       <c r="K18">
-        <v>109.23076923076923</v>
+        <v>133.39920000000001</v>
       </c>
       <c r="L18" s="4">
-        <v>133.39920000000001</v>
-      </c>
-      <c r="M18" s="1">
-        <v>2.767756780981208</v>
-      </c>
-      <c r="N18" s="1"/>
+        <v>2.767757</v>
+      </c>
+      <c r="M18" s="4"/>
+      <c r="N18">
+        <v>37532.631580000001</v>
+      </c>
       <c r="O18">
-        <v>37532.631578947367</v>
+        <v>96</v>
       </c>
       <c r="P18">
-        <v>96</v>
+        <v>3603133</v>
       </c>
       <c r="Q18">
-        <f>O18*P18</f>
-        <v>3603132.6315789474</v>
-      </c>
-      <c r="R18" s="10">
-        <f t="shared" si="2"/>
-        <v>6.5566802488288403</v>
+        <v>6.5566800000000001</v>
+      </c>
+      <c r="R18">
+        <v>0.163934</v>
       </c>
       <c r="S18">
-        <v>0.16393405706926287</v>
-      </c>
-      <c r="T18" s="10">
-        <f t="shared" si="3"/>
-        <v>590676.15045338648</v>
-      </c>
-      <c r="U18" s="10">
-        <f t="shared" si="4"/>
-        <v>5.7713494358390021</v>
+        <v>590676.19999999995</v>
+      </c>
+      <c r="T18">
+        <v>5.7713489999999998</v>
+      </c>
+      <c r="U18">
+        <v>6.5</v>
       </c>
       <c r="V18">
-        <v>0.75732990722515481</v>
-      </c>
-      <c r="W18" s="10">
-        <f t="shared" si="5"/>
-        <v>2728760.1015936122</v>
-      </c>
-      <c r="X18" s="10">
-        <f t="shared" si="6"/>
-        <v>6.4359653564343713</v>
+        <v>5.0599999999999996</v>
+      </c>
+      <c r="W18">
+        <v>7.1</v>
+      </c>
+      <c r="X18">
+        <v>6.75</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1899,62 +1801,56 @@
         <v>28</v>
       </c>
       <c r="G19" t="s">
-        <v>99</v>
-      </c>
-      <c r="H19" s="2">
+        <v>97</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19">
         <v>0</v>
       </c>
-      <c r="J19" s="2">
-        <v>0</v>
+      <c r="J19">
+        <v>105.5556</v>
       </c>
       <c r="K19">
-        <v>105.55555555555556</v>
+        <v>113.63639999999999</v>
       </c>
       <c r="L19" s="4">
-        <v>113.63639999999999</v>
-      </c>
-      <c r="M19" s="1">
-        <v>2.3869446243705745</v>
-      </c>
-      <c r="N19" s="1"/>
+        <v>2.3869449999999999</v>
+      </c>
+      <c r="M19" s="4"/>
+      <c r="N19">
+        <v>60924.452380000002</v>
+      </c>
       <c r="O19">
-        <v>60924.452380952382</v>
+        <v>86</v>
       </c>
       <c r="P19">
-        <v>86</v>
+        <v>5239503</v>
       </c>
       <c r="Q19">
-        <f>O19*P19</f>
-        <v>5239502.9047619049</v>
-      </c>
-      <c r="R19" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7192900854647215</v>
+        <v>6.71929</v>
+      </c>
+      <c r="R19">
+        <v>0.106672</v>
       </c>
       <c r="S19">
-        <v>0.10667194421571763</v>
-      </c>
-      <c r="T19" s="10">
-        <f t="shared" si="3"/>
-        <v>558907.96157485235</v>
-      </c>
-      <c r="U19" s="10">
-        <f t="shared" si="4"/>
-        <v>5.7473402961311999</v>
+        <v>558908</v>
+      </c>
+      <c r="T19">
+        <v>5.7473400000000003</v>
+      </c>
+      <c r="U19">
+        <v>5.4</v>
       </c>
       <c r="V19">
-        <v>0.72856188329412186</v>
-      </c>
-      <c r="W19" s="10">
-        <f t="shared" si="5"/>
-        <v>3817302.1038183556</v>
-      </c>
-      <c r="X19" s="10">
-        <f t="shared" si="6"/>
-        <v>6.5817565316623368</v>
+        <v>2.86</v>
+      </c>
+      <c r="W19">
+        <v>5.7</v>
+      </c>
+      <c r="X19">
+        <v>3.25</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -1973,22 +1869,28 @@
       <c r="G20" t="s">
         <v>73</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20">
         <v>511</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20">
         <v>541</v>
       </c>
-      <c r="J20" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0587084148727985</v>
-      </c>
-      <c r="M20">
-        <v>1.6893088591236203</v>
-      </c>
-      <c r="N20" s="1"/>
-      <c r="W20"/>
-      <c r="X20"/>
+      <c r="L20">
+        <v>1.6893089999999999</v>
+      </c>
+      <c r="M20" s="4"/>
+      <c r="S20" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T20" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="W20">
+        <v>6.6</v>
+      </c>
+      <c r="X20">
+        <v>5.52</v>
+      </c>
     </row>
     <row r="21" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
@@ -2006,133 +1908,114 @@
       <c r="G21" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21">
         <v>574</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21">
         <v>86</v>
       </c>
-      <c r="J21" s="2">
-        <f t="shared" si="1"/>
-        <v>0.14982578397212543</v>
-      </c>
-      <c r="M21">
-        <v>2.5814376192313899</v>
-      </c>
-      <c r="N21" s="1"/>
+      <c r="L21">
+        <v>2.5814379999999999</v>
+      </c>
+      <c r="M21" s="4"/>
+      <c r="N21">
+        <v>51494.515149999999</v>
+      </c>
       <c r="O21">
-        <v>51494.515151515152</v>
+        <v>65</v>
       </c>
       <c r="P21">
-        <v>65</v>
+        <v>3347143</v>
       </c>
       <c r="Q21">
-        <f t="shared" ref="Q21:Q27" si="7">O21*P21</f>
-        <v>3347143.4848484849</v>
-      </c>
-      <c r="R21" s="10">
-        <f t="shared" si="2"/>
-        <v>6.5246743300280095</v>
+        <v>6.5246740000000001</v>
+      </c>
+      <c r="R21">
+        <v>0.69147199999999998</v>
       </c>
       <c r="S21">
-        <v>0.69147187383040953</v>
-      </c>
-      <c r="T21" s="10">
-        <f t="shared" si="3"/>
-        <v>2314455.5774474288</v>
-      </c>
-      <c r="U21" s="10">
-        <f t="shared" si="4"/>
-        <v>6.3644488495584071</v>
-      </c>
-      <c r="V21">
-        <v>0.24596055941149852</v>
-      </c>
-      <c r="W21" s="10">
-        <f t="shared" si="5"/>
-        <v>823265.28396388597</v>
-      </c>
-      <c r="X21" s="10">
-        <f t="shared" si="6"/>
-        <v>5.9155398021589978</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" s="5" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+        <v>2314456</v>
+      </c>
+      <c r="T21">
+        <v>6.3644489999999996</v>
+      </c>
+      <c r="W21">
+        <v>4.3</v>
+      </c>
+      <c r="X21">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" t="s">
         <v>88</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" t="s">
         <v>68</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" t="s">
         <v>30</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" t="s">
         <v>71</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22">
         <v>318</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22">
         <v>74</v>
       </c>
-      <c r="J22" s="6">
-        <f t="shared" si="1"/>
-        <v>0.23270440251572327</v>
-      </c>
-      <c r="K22" s="5">
-        <v>101.35135135135134</v>
-      </c>
-      <c r="L22" s="7">
+      <c r="J22">
+        <v>101.3514</v>
+      </c>
+      <c r="K22">
         <v>112.5926</v>
       </c>
-      <c r="M22" s="8">
-        <v>1.6935510855959135</v>
-      </c>
-      <c r="N22" s="9"/>
-      <c r="O22" s="5">
-        <v>156623.86363636365</v>
-      </c>
-      <c r="P22" s="5">
+      <c r="L22" s="4">
+        <v>1.693551</v>
+      </c>
+      <c r="M22" s="4"/>
+      <c r="N22">
+        <v>156623.86360000001</v>
+      </c>
+      <c r="O22">
         <v>94</v>
       </c>
-      <c r="Q22" s="5">
-        <f t="shared" si="7"/>
-        <v>14722643.181818184</v>
-      </c>
-      <c r="R22" s="5">
-        <f t="shared" si="2"/>
-        <v>7.1679857866474146</v>
-      </c>
-      <c r="S22" s="5">
+      <c r="P22">
+        <v>14722643</v>
+      </c>
+      <c r="Q22">
+        <v>7.167986</v>
+      </c>
+      <c r="R22">
         <v>0</v>
       </c>
-      <c r="T22" s="5">
-        <f t="shared" si="3"/>
+      <c r="S22">
         <v>0</v>
       </c>
-      <c r="U22" s="5">
+      <c r="T22">
         <v>0</v>
       </c>
-      <c r="V22" s="5">
-        <v>0.45145901169439256</v>
-      </c>
-      <c r="W22" s="5">
-        <f t="shared" si="5"/>
-        <v>6646669.9403928239</v>
-      </c>
-      <c r="X22" s="5">
-        <f t="shared" si="6"/>
-        <v>6.8226041131618205</v>
+      <c r="U22">
+        <v>7.4</v>
+      </c>
+      <c r="V22">
+        <v>6.75</v>
+      </c>
+      <c r="W22">
+        <v>7.5</v>
+      </c>
+      <c r="X22">
+        <v>7.6</v>
       </c>
     </row>
     <row r="23" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2157,61 +2040,54 @@
       <c r="G23" t="s">
         <v>72</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23">
         <v>531</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23">
         <v>539</v>
       </c>
-      <c r="J23" s="2">
-        <f t="shared" si="1"/>
-        <v>1.0150659133709981</v>
+      <c r="J23">
+        <v>101.7544</v>
       </c>
       <c r="K23">
-        <v>101.75438596491226</v>
+        <v>109.4395</v>
       </c>
       <c r="L23" s="4">
-        <v>109.4395</v>
-      </c>
-      <c r="M23" s="3">
-        <v>2.8424781827098919</v>
-      </c>
-      <c r="N23" s="1"/>
+        <v>2.8424779999999998</v>
+      </c>
+      <c r="M23" s="4"/>
+      <c r="N23">
+        <v>62909.787230000002</v>
+      </c>
       <c r="O23">
-        <v>62909.787234042553</v>
+        <v>86</v>
       </c>
       <c r="P23">
-        <v>86</v>
+        <v>5410242</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="7"/>
-        <v>5410241.7021276597</v>
-      </c>
-      <c r="R23" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7332166676122087</v>
+        <v>6.7332169999999998</v>
+      </c>
+      <c r="R23">
+        <v>0.54083800000000004</v>
       </c>
       <c r="S23">
-        <v>0.54083807836254028</v>
-      </c>
-      <c r="T23" s="10">
-        <f t="shared" si="3"/>
-        <v>2926064.7256556023</v>
-      </c>
-      <c r="U23" s="10">
-        <f t="shared" si="4"/>
-        <v>6.4662839286533256</v>
+        <v>2926065</v>
+      </c>
+      <c r="T23">
+        <v>6.4662839999999999</v>
+      </c>
+      <c r="U23">
+        <v>5.7</v>
       </c>
       <c r="V23">
-        <v>0.41048175825290062</v>
-      </c>
-      <c r="W23" s="10">
-        <f t="shared" si="5"/>
-        <v>2220805.5264625275</v>
-      </c>
-      <c r="X23" s="10">
-        <f t="shared" si="6"/>
-        <v>6.3465105295155722</v>
+        <v>3.39</v>
+      </c>
+      <c r="W23">
+        <v>5.8</v>
+      </c>
+      <c r="X23">
+        <v>3.71</v>
       </c>
     </row>
     <row r="24" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2234,63 +2110,56 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>98</v>
-      </c>
-      <c r="H24" s="2">
+        <v>96</v>
+      </c>
+      <c r="H24">
         <v>573</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24">
         <v>344</v>
       </c>
-      <c r="J24" s="2">
-        <f t="shared" si="1"/>
-        <v>0.6003490401396161</v>
+      <c r="J24">
+        <v>106.66670000000001</v>
       </c>
       <c r="K24">
-        <v>106.66666666666667</v>
+        <v>127.1523</v>
       </c>
       <c r="L24" s="4">
-        <v>127.1523</v>
-      </c>
-      <c r="M24" s="1">
-        <v>3.1480440051622276</v>
-      </c>
-      <c r="N24" s="1"/>
+        <v>3.1480440000000001</v>
+      </c>
+      <c r="M24" s="4"/>
+      <c r="N24">
+        <v>88131.477270000003</v>
+      </c>
       <c r="O24">
-        <v>88131.477272727279</v>
+        <v>90</v>
       </c>
       <c r="P24">
-        <v>90</v>
+        <v>7931833</v>
       </c>
       <c r="Q24">
-        <f t="shared" si="7"/>
-        <v>7931832.9545454551</v>
-      </c>
-      <c r="R24" s="10">
-        <f t="shared" si="2"/>
-        <v>6.8993735593301571</v>
+        <v>6.8993739999999999</v>
+      </c>
+      <c r="R24">
+        <v>0.12582499999999999</v>
       </c>
       <c r="S24">
-        <v>0.12582524547228782</v>
-      </c>
-      <c r="T24" s="10">
-        <f t="shared" si="3"/>
-        <v>998024.82855086389</v>
-      </c>
-      <c r="U24" s="10">
-        <f t="shared" si="4"/>
-        <v>5.9991413456646319</v>
+        <v>998024.8</v>
+      </c>
+      <c r="T24">
+        <v>5.9991409999999998</v>
+      </c>
+      <c r="U24">
+        <v>6</v>
       </c>
       <c r="V24">
-        <v>0.75373302172903855</v>
-      </c>
-      <c r="W24" s="10">
-        <f t="shared" si="5"/>
-        <v>5978484.4206795134</v>
-      </c>
-      <c r="X24" s="10">
-        <f t="shared" si="6"/>
-        <v>6.7765911018548994</v>
+        <v>4.53</v>
+      </c>
+      <c r="W24">
+        <v>6.4</v>
+      </c>
+      <c r="X24">
+        <v>5.76</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2313,63 +2182,56 @@
         <v>28</v>
       </c>
       <c r="G25" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="2">
+        <v>97</v>
+      </c>
+      <c r="H25">
         <v>508</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25">
         <v>539</v>
       </c>
-      <c r="J25" s="2">
-        <f t="shared" si="1"/>
-        <v>1.061023622047244</v>
+      <c r="J25">
+        <v>102</v>
       </c>
       <c r="K25">
-        <v>102</v>
+        <v>93.971630000000005</v>
       </c>
       <c r="L25" s="4">
-        <v>93.971630000000005</v>
-      </c>
-      <c r="M25" s="1">
-        <v>2.5023041890551116</v>
-      </c>
-      <c r="N25" s="1"/>
+        <v>2.5023040000000001</v>
+      </c>
+      <c r="M25" s="4"/>
+      <c r="N25">
+        <v>50784.307690000001</v>
+      </c>
       <c r="O25">
-        <v>50784.307692307695</v>
+        <v>79</v>
       </c>
       <c r="P25">
-        <v>79</v>
+        <v>4011960</v>
       </c>
       <c r="Q25">
-        <f t="shared" si="7"/>
-        <v>4011960.307692308</v>
-      </c>
-      <c r="R25" s="10">
-        <f t="shared" si="2"/>
-        <v>6.6033566276795179</v>
+        <v>6.6033569999999999</v>
+      </c>
+      <c r="R25">
+        <v>0.13689200000000001</v>
       </c>
       <c r="S25">
-        <v>0.1368921081644244</v>
-      </c>
-      <c r="T25" s="10">
-        <f t="shared" si="3"/>
-        <v>549205.70439199288</v>
-      </c>
-      <c r="U25" s="10">
-        <f t="shared" si="4"/>
-        <v>5.7397350394407178</v>
+        <v>549205.69999999995</v>
+      </c>
+      <c r="T25">
+        <v>5.7397349999999996</v>
+      </c>
+      <c r="U25">
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>0.75858232501518019</v>
-      </c>
-      <c r="W25" s="10">
-        <f t="shared" si="5"/>
-        <v>3043402.1780778486</v>
-      </c>
-      <c r="X25" s="10">
-        <f t="shared" si="6"/>
-        <v>6.4833593470932165</v>
+        <v>2.82</v>
+      </c>
+      <c r="W25">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="X25">
+        <v>2.65</v>
       </c>
     </row>
     <row r="26" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2392,63 +2254,56 @@
         <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="2">
+        <v>96</v>
+      </c>
+      <c r="H26">
         <v>381</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26">
         <v>101</v>
       </c>
-      <c r="J26" s="2">
-        <f t="shared" si="1"/>
-        <v>0.26509186351706038</v>
+      <c r="J26">
+        <v>109.0909</v>
       </c>
       <c r="K26">
-        <v>109.09090909090908</v>
+        <v>131.81819999999999</v>
       </c>
       <c r="L26" s="4">
-        <v>131.81819999999999</v>
-      </c>
-      <c r="M26" s="1">
-        <v>2.619948549257999</v>
-      </c>
-      <c r="N26" s="1"/>
+        <v>2.6199490000000001</v>
+      </c>
+      <c r="M26" s="4"/>
+      <c r="N26">
+        <v>54532.620690000003</v>
+      </c>
       <c r="O26">
-        <v>54532.620689655174</v>
+        <v>61</v>
       </c>
       <c r="P26">
-        <v>61</v>
+        <v>3326490</v>
       </c>
       <c r="Q26">
-        <f t="shared" si="7"/>
-        <v>3326489.8620689656</v>
-      </c>
-      <c r="R26" s="10">
-        <f t="shared" si="2"/>
-        <v>6.5219862042124861</v>
+        <v>6.5219860000000001</v>
+      </c>
+      <c r="R26">
+        <v>0.35286899999999999</v>
       </c>
       <c r="S26">
-        <v>0.35286940743601902</v>
-      </c>
-      <c r="T26" s="10">
-        <f t="shared" si="3"/>
-        <v>1173816.5064702006</v>
-      </c>
-      <c r="U26" s="10">
-        <f t="shared" si="4"/>
-        <v>6.0696002123666153</v>
+        <v>1173817</v>
+      </c>
+      <c r="T26">
+        <v>6.0696000000000003</v>
+      </c>
+      <c r="U26">
+        <v>5.5</v>
       </c>
       <c r="V26">
-        <v>0.61482562233325599</v>
-      </c>
-      <c r="W26" s="10">
-        <f t="shared" si="5"/>
-        <v>2045211.1996318186</v>
-      </c>
-      <c r="X26" s="10">
-        <f t="shared" si="6"/>
-        <v>6.3107381622693346</v>
+        <v>3.3</v>
+      </c>
+      <c r="W26">
+        <v>6</v>
+      </c>
+      <c r="X26">
+        <v>4.3499999999999996</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2471,62 +2326,56 @@
         <v>28</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
-      </c>
-      <c r="H27" s="2">
+        <v>97</v>
+      </c>
+      <c r="H27">
         <v>0</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27">
         <v>0</v>
       </c>
-      <c r="J27" s="2">
-        <v>0</v>
+      <c r="J27">
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>99.28058</v>
       </c>
       <c r="L27" s="4">
-        <v>99.28058</v>
-      </c>
-      <c r="M27" s="1">
-        <v>2.5090949438113794</v>
-      </c>
-      <c r="N27" s="1"/>
+        <v>2.5090949999999999</v>
+      </c>
+      <c r="M27" s="4"/>
+      <c r="N27">
+        <v>23308.625</v>
+      </c>
       <c r="O27">
-        <v>23308.625</v>
+        <v>64</v>
       </c>
       <c r="P27">
-        <v>64</v>
+        <v>1491752</v>
       </c>
       <c r="Q27">
-        <f t="shared" si="7"/>
-        <v>1491752</v>
-      </c>
-      <c r="R27" s="10">
-        <f t="shared" si="2"/>
-        <v>6.1736966287774937</v>
+        <v>6.1736969999999998</v>
+      </c>
+      <c r="R27">
+        <v>0.146064</v>
       </c>
       <c r="S27">
-        <v>0.1460637709096112</v>
-      </c>
-      <c r="T27" s="10">
-        <f t="shared" si="3"/>
-        <v>217890.92238195433</v>
-      </c>
-      <c r="U27" s="10">
-        <f t="shared" si="4"/>
-        <v>5.3382391373525113</v>
+        <v>217890.9</v>
+      </c>
+      <c r="T27">
+        <v>5.3382389999999997</v>
+      </c>
+      <c r="U27">
+        <v>4</v>
       </c>
       <c r="V27">
-        <v>0.75586451450771674</v>
-      </c>
-      <c r="W27" s="10">
-        <f t="shared" si="5"/>
-        <v>1127562.4012459156</v>
-      </c>
-      <c r="X27" s="10">
-        <f t="shared" si="6"/>
-        <v>6.0521405858199371</v>
+        <v>1.39</v>
+      </c>
+      <c r="W27">
+        <v>4</v>
+      </c>
+      <c r="X27">
+        <v>1.38</v>
       </c>
     </row>
     <row r="28" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2551,28 +2400,40 @@
       <c r="G28" t="s">
         <v>75</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28">
         <v>45</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28">
         <v>24</v>
       </c>
-      <c r="J28" s="2">
-        <f t="shared" si="1"/>
-        <v>0.53333333333333333</v>
+      <c r="J28">
+        <v>117.2414</v>
       </c>
       <c r="K28">
-        <v>117.24137931034481</v>
+        <v>179.78720000000001</v>
       </c>
       <c r="L28" s="4">
-        <v>179.78720000000001</v>
-      </c>
-      <c r="M28" s="1">
-        <v>2.0773315611289904</v>
-      </c>
-      <c r="N28" s="1"/>
-      <c r="W28"/>
-      <c r="X28"/>
+        <v>2.0773320000000002</v>
+      </c>
+      <c r="M28" s="4"/>
+      <c r="S28" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="T28" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U28">
+        <v>5.8</v>
+      </c>
+      <c r="V28">
+        <v>3.76</v>
+      </c>
+      <c r="W28">
+        <v>6.8</v>
+      </c>
+      <c r="X28">
+        <v>6.76</v>
+      </c>
     </row>
     <row r="29" spans="1:24" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -2596,61 +2457,54 @@
       <c r="G29" t="s">
         <v>76</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29">
         <v>480</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29">
         <v>266</v>
       </c>
-      <c r="J29" s="2">
-        <f t="shared" si="1"/>
-        <v>0.5541666666666667</v>
+      <c r="J29">
+        <v>103.9216</v>
       </c>
       <c r="K29">
-        <v>103.92156862745099</v>
+        <v>105.9289</v>
       </c>
       <c r="L29" s="4">
-        <v>105.92885375494072</v>
-      </c>
-      <c r="M29" s="1">
-        <v>2.8049908234762881</v>
-      </c>
-      <c r="N29" s="1"/>
+        <v>2.8049909999999998</v>
+      </c>
+      <c r="M29" s="4"/>
+      <c r="N29">
+        <v>89522.113639999996</v>
+      </c>
       <c r="O29">
-        <v>89522.113636363632</v>
+        <v>82</v>
       </c>
       <c r="P29">
-        <v>82</v>
+        <v>7340813</v>
       </c>
       <c r="Q29">
-        <f>O29*P29</f>
-        <v>7340813.3181818174</v>
-      </c>
-      <c r="R29" s="10">
-        <f t="shared" si="2"/>
-        <v>6.8657441798112151</v>
+        <v>6.8657440000000003</v>
+      </c>
+      <c r="R29">
+        <v>0.56993099999999997</v>
       </c>
       <c r="S29">
-        <v>0.56993129905820983</v>
-      </c>
-      <c r="T29" s="10">
-        <f t="shared" si="3"/>
-        <v>4183759.2705751709</v>
-      </c>
-      <c r="U29" s="10">
-        <f t="shared" si="4"/>
-        <v>6.6215666876975172</v>
+        <v>4183759</v>
+      </c>
+      <c r="T29">
+        <v>6.6215669999999998</v>
+      </c>
+      <c r="U29">
+        <v>5.0999999999999996</v>
       </c>
       <c r="V29">
-        <v>0.3779629359469191</v>
-      </c>
-      <c r="W29" s="10">
-        <f t="shared" si="5"/>
-        <v>2774555.3539782451</v>
-      </c>
-      <c r="X29" s="10">
-        <f t="shared" si="6"/>
-        <v>6.4431933936618071</v>
+        <v>2.5299999999999998</v>
+      </c>
+      <c r="W29">
+        <v>5.3</v>
+      </c>
+      <c r="X29">
+        <v>2.68</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2673,63 +2527,56 @@
         <v>27</v>
       </c>
       <c r="G30" t="s">
-        <v>98</v>
-      </c>
-      <c r="H30" s="2">
+        <v>96</v>
+      </c>
+      <c r="H30">
         <v>468</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30">
         <v>565</v>
       </c>
-      <c r="J30" s="2">
-        <f t="shared" si="1"/>
-        <v>1.2072649572649572</v>
+      <c r="J30">
+        <v>107.0175</v>
       </c>
       <c r="K30">
-        <v>107.01754385964912</v>
+        <v>118.5864</v>
       </c>
       <c r="L30" s="4">
-        <v>118.5864</v>
-      </c>
-      <c r="M30" s="1">
-        <v>3.0309800184242359</v>
-      </c>
-      <c r="N30" s="1"/>
+        <v>3.03098</v>
+      </c>
+      <c r="M30" s="4"/>
+      <c r="N30">
+        <v>68515.05</v>
+      </c>
       <c r="O30">
-        <v>68515.05</v>
+        <v>81</v>
       </c>
       <c r="P30">
-        <v>81</v>
+        <v>5549719</v>
       </c>
       <c r="Q30">
-        <f>O30*P30</f>
-        <v>5549719.0499999998</v>
-      </c>
-      <c r="R30" s="10">
-        <f t="shared" si="2"/>
-        <v>6.7442709978752715</v>
+        <v>6.7442710000000003</v>
+      </c>
+      <c r="R30">
+        <v>0.43455899999999997</v>
       </c>
       <c r="S30">
-        <v>0.43455928403927446</v>
-      </c>
-      <c r="T30" s="10">
-        <f t="shared" si="3"/>
-        <v>2411681.9369871225</v>
-      </c>
-      <c r="U30" s="10">
-        <f t="shared" si="4"/>
-        <v>6.3823200306158006</v>
+        <v>2411682</v>
+      </c>
+      <c r="T30">
+        <v>6.38232</v>
+      </c>
+      <c r="U30">
+        <v>5.7</v>
       </c>
       <c r="V30">
-        <v>0.51723610733643088</v>
-      </c>
-      <c r="W30" s="10">
-        <f t="shared" si="5"/>
-        <v>2870515.078232835</v>
-      </c>
-      <c r="X30" s="10">
-        <f t="shared" si="6"/>
-        <v>6.4579598324703573</v>
+        <v>3.82</v>
+      </c>
+      <c r="W30">
+        <v>6.1</v>
+      </c>
+      <c r="X30">
+        <v>4.53</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2752,63 +2599,56 @@
         <v>28</v>
       </c>
       <c r="G31" t="s">
-        <v>99</v>
-      </c>
-      <c r="H31" s="2">
+        <v>97</v>
+      </c>
+      <c r="H31">
         <v>274</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
+      <c r="J31">
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>98.818899999999999</v>
       </c>
       <c r="L31" s="4">
-        <v>98.818899999999999</v>
-      </c>
-      <c r="M31" s="3">
-        <v>2.8089735266532672</v>
-      </c>
-      <c r="N31" s="1"/>
+        <v>2.8089740000000001</v>
+      </c>
+      <c r="M31" s="4"/>
+      <c r="N31">
+        <v>28706.44</v>
+      </c>
       <c r="O31">
-        <v>28706.44</v>
+        <v>50</v>
       </c>
       <c r="P31">
-        <v>50</v>
+        <v>1435322</v>
       </c>
       <c r="Q31">
-        <f>O31*P31</f>
-        <v>1435322</v>
-      </c>
-      <c r="R31" s="10">
-        <f t="shared" si="2"/>
-        <v>6.1569493415827896</v>
+        <v>6.156949</v>
+      </c>
+      <c r="R31">
+        <v>9.6317E-2</v>
       </c>
       <c r="S31">
-        <v>9.6317372452167621E-2</v>
-      </c>
-      <c r="T31" s="10">
-        <f t="shared" si="3"/>
-        <v>138246.44366279015</v>
-      </c>
-      <c r="U31" s="10">
-        <f t="shared" si="4"/>
-        <v>5.1406539680599792</v>
+        <v>138246.39999999999</v>
+      </c>
+      <c r="T31">
+        <v>5.1406539999999996</v>
+      </c>
+      <c r="U31">
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>0.82418173681734175</v>
-      </c>
-      <c r="W31" s="10">
-        <f t="shared" si="5"/>
-        <v>1182966.1788521407</v>
-      </c>
-      <c r="X31" s="10">
-        <f t="shared" si="6"/>
-        <v>6.072972328273023</v>
+        <v>2.54</v>
+      </c>
+      <c r="W31">
+        <v>5</v>
+      </c>
+      <c r="X31">
+        <v>2.5099999999999998</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2831,63 +2671,56 @@
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>98</v>
-      </c>
-      <c r="H32" s="2">
+        <v>96</v>
+      </c>
+      <c r="H32">
         <v>582</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32">
         <v>125</v>
       </c>
-      <c r="J32" s="2">
-        <f t="shared" si="1"/>
-        <v>0.21477663230240548</v>
+      <c r="J32">
+        <v>101.2821</v>
       </c>
       <c r="K32">
-        <v>101.2820512820513</v>
+        <v>101.3189</v>
       </c>
       <c r="L32" s="4">
-        <v>101.3189</v>
-      </c>
-      <c r="M32" s="3">
-        <v>2.18135759202845</v>
-      </c>
-      <c r="N32" s="1"/>
+        <v>2.1813579999999999</v>
+      </c>
+      <c r="M32" s="4"/>
+      <c r="N32">
+        <v>101500.6744</v>
+      </c>
       <c r="O32">
-        <v>101500.67441860466</v>
+        <v>87</v>
       </c>
       <c r="P32">
-        <v>87</v>
+        <v>8830559</v>
       </c>
       <c r="Q32">
-        <f>O32*P32</f>
-        <v>8830558.6744186059</v>
-      </c>
-      <c r="R32" s="10">
-        <f t="shared" si="2"/>
-        <v>6.9459881805358838</v>
+        <v>6.9459879999999998</v>
+      </c>
+      <c r="R32">
+        <v>0.163799</v>
       </c>
       <c r="S32">
-        <v>0.16379850795876322</v>
-      </c>
-      <c r="T32" s="10">
-        <f t="shared" si="3"/>
-        <v>1446432.3353120815</v>
-      </c>
-      <c r="U32" s="10">
-        <f t="shared" si="4"/>
-        <v>6.1602981219882009</v>
+        <v>1446432</v>
+      </c>
+      <c r="T32">
+        <v>6.1602980000000001</v>
+      </c>
+      <c r="U32">
+        <v>7.8</v>
       </c>
       <c r="V32">
-        <v>0.73849105644906288</v>
-      </c>
-      <c r="W32" s="10">
-        <f t="shared" si="5"/>
-        <v>6521288.6045068325</v>
-      </c>
-      <c r="X32" s="10">
-        <f t="shared" si="6"/>
-        <v>6.8143334206600334</v>
+        <v>8.34</v>
+      </c>
+      <c r="W32">
+        <v>7.9</v>
+      </c>
+      <c r="X32">
+        <v>8.4499999999999993</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="16" x14ac:dyDescent="0.2">
@@ -2910,63 +2743,56 @@
         <v>28</v>
       </c>
       <c r="G33" t="s">
-        <v>99</v>
-      </c>
-      <c r="H33" s="2">
+        <v>97</v>
+      </c>
+      <c r="H33">
         <v>590</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33">
         <v>152</v>
       </c>
-      <c r="J33" s="2">
-        <f t="shared" si="1"/>
-        <v>0.25762711864406779</v>
+      <c r="J33">
+        <v>103.7037</v>
       </c>
       <c r="K33">
-        <v>103.7037037037037</v>
+        <v>102.8777</v>
       </c>
       <c r="L33" s="4">
-        <v>102.8777</v>
-      </c>
-      <c r="M33" s="1">
-        <v>2.8791761907363385</v>
-      </c>
-      <c r="N33" s="1"/>
+        <v>2.8791760000000002</v>
+      </c>
+      <c r="M33" s="4"/>
+      <c r="N33">
+        <v>57581</v>
+      </c>
       <c r="O33">
-        <v>57581</v>
+        <v>46</v>
       </c>
       <c r="P33">
-        <v>46</v>
+        <v>2648726</v>
       </c>
       <c r="Q33">
-        <f>O33*P33</f>
-        <v>2648726</v>
-      </c>
-      <c r="R33" s="10">
-        <f t="shared" si="2"/>
-        <v>6.4230370346118058</v>
+        <v>6.4230369999999999</v>
+      </c>
+      <c r="R33">
+        <v>0.46686100000000003</v>
       </c>
       <c r="S33">
-        <v>0.46686103545362972</v>
-      </c>
-      <c r="T33" s="10">
-        <f t="shared" si="3"/>
-        <v>1236586.9629929508</v>
-      </c>
-      <c r="U33" s="10">
-        <f t="shared" si="4"/>
-        <v>6.0922246635359212</v>
+        <v>1236587</v>
+      </c>
+      <c r="T33">
+        <v>6.092225</v>
+      </c>
+      <c r="U33">
+        <v>5.4</v>
       </c>
       <c r="V33">
-        <v>0.48561341122818136</v>
-      </c>
-      <c r="W33" s="10">
-        <f t="shared" si="5"/>
-        <v>1286256.868268776</v>
-      </c>
-      <c r="X33" s="10">
-        <f t="shared" si="6"/>
-        <v>6.1093277067934366</v>
+        <v>2.78</v>
+      </c>
+      <c r="W33">
+        <v>5.6</v>
+      </c>
+      <c r="X33">
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>
